--- a/site/exports/nwpu-foreignstudies.xlsx
+++ b/site/exports/nwpu-foreignstudies.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,8 +622,61 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>外国语学院</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期未单独记录；来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Combined highest-degree OR final-education field does not explicitly establish award; degree_awarded remains null. Literal 199111 is unparsed; every education/award date remains unknown.；No personal mentorship evidence or advisor edge.；CV stale present-tense appointment and reversed teaching interval 201509-201412 are not integrated; current employment unknown and navigation disabled.；Two titles are official-CV bibliographic labels only; year, publisher, authorship role and original-language title unknown; no external metadata or full-text verification.；Original CV bytes and rendered screenshots are not newly copied into this handoff; retained minimal extraction/visual report is the retained evidence.；来源记载职业信息：职业身份表述：来源表述：教授；来源说明：Professional-title field in undated CV; not independent verification of current employment or an appointment date.。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：全球化与跨国民族主义理论；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源教学终点：未知；Course name only; no chronology or current teaching assertion.；来源ID：new-recovery-nwpu-yin-xiaohuang-s002-8ba55e181abe；https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C | 全球化视野下的美国和东亚；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源教学终点：未知；Course name only; no chronology or current teaching assertion.；来源ID：new-recovery-nwpu-yin-xiaohuang-s002-8ba55e181abe；https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C | 美国研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源教学终点：未知；Course name only; no chronology or current teaching assertion.；来源ID：new-recovery-nwpu-yin-xiaohuang-s002-8ba55e181abe；https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>原来源入口为官方人物资料入口页（本轮未重新读取附件正文），不作为独立个人主页展示；此分类不表示链接当前不可用。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>官方人物资料入口页（本轮未重新读取附件正文）：https://wgyxy.nwpu.edu.cn/info/1045/2291.htm</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -638,11 +691,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="23.8" customWidth="1" min="2" max="2"/>
+    <col width="54.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -657,7 +710,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="60.2" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -720,7 +773,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1523,8 +1576,65 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>highest_degree_or_final_education_label</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>哈佛大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Mixed highest-degree OR final-education field supports only the doctorate label and reported institution/department. No explicit award statement. Literal 199111 is not parsed as 1991-11, year 1991, a footnote, or any date.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（院系）：美国研究系</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S13"/>
+  <autoFilter ref="A1:S14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1538,6 +1648,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1640,18 +1751,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="60.2" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="60.2" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="61.59999999999999" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1927,8 +2038,100 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>美国华裔文学史</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；Chinese title label as reported in official CV; no original English title, year, publisher, author order or role inferred.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>美籍华人与中美关系</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；Chinese title label as reported in official CV; no original English title, year, publisher, author order or role inferred.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1938,6 +2141,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1949,14 +2156,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2257,8 +2464,148 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-yin-xiaohuang-s001-97df3e97788f</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/szdw/jsfc/js.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T19:39:54Z</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-yin-xiaohuang-s002-8ba55e181abe</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/system/_content/download.jsp?urltype=news.DownloadAttachUrl&amp;owner=1843571494&amp;wbfileid=037D081CCBC36796D4C3D1197100768C</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-yin-xiaohuang-s003-926324fb9916</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/info/1045/2291.htm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T19:40:03Z</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>尹晓煌</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-yin-xiaohuang-s004-926324fb9916</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://wgyxy.nwpu.edu.cn/info/1045/2291.htm</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2267,6 +2614,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
